--- a/data/trans_dic/P0902-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P0902-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejó de hacer algunas tareas por problemas físicos</t>
+          <t>Población que dejó de hacer algunas tareas por problemas físicos (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,08; 10,33</t>
+          <t>5,11; 10,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,81; 8,76</t>
+          <t>3,73; 8,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,47; 10,73</t>
+          <t>5,42; 10,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,86; 10,47</t>
+          <t>5,88; 10,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,5; 16,18</t>
+          <t>8,41; 15,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,43; 16,1</t>
+          <t>8,29; 16,12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,58; 15,15</t>
+          <t>7,65; 15,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,75; 15,02</t>
+          <t>9,81; 15,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,15; 11,2</t>
+          <t>6,96; 11,32</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,4; 10,83</t>
+          <t>6,37; 10,61</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,31; 11,72</t>
+          <t>7,11; 11,51</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,29; 11,73</t>
+          <t>8,42; 11,86</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,12; 8,28</t>
+          <t>3,17; 7,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,41; 14,1</t>
+          <t>7,43; 13,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,51; 8,43</t>
+          <t>3,76; 8,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,54; 12,19</t>
+          <t>6,63; 12,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,33; 12,33</t>
+          <t>6,41; 12,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,74; 14,88</t>
+          <t>7,78; 14,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,73; 13,7</t>
+          <t>6,71; 13,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,72; 16,08</t>
+          <t>10,75; 16,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,4; 9,45</t>
+          <t>5,4; 9,28</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,32; 12,96</t>
+          <t>8,32; 13,01</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,59; 9,77</t>
+          <t>5,86; 9,88</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,17; 12,96</t>
+          <t>9,16; 12,88</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,55; 9,96</t>
+          <t>5,58; 9,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,06; 16,84</t>
+          <t>10,81; 16,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,72; 11,88</t>
+          <t>6,51; 11,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,43; 16,37</t>
+          <t>3,42; 16,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,2; 25,48</t>
+          <t>13,71; 25,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,99; 25,2</t>
+          <t>14,91; 25,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,14; 29,57</t>
+          <t>15,67; 29,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,15; 29,08</t>
+          <t>18,13; 29,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,06; 12,33</t>
+          <t>8,1; 12,58</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12,99; 17,89</t>
+          <t>12,86; 18,19</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,98; 15,05</t>
+          <t>10,08; 15,15</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,85; 18,04</t>
+          <t>4,84; 17,97</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,61; 11,89</t>
+          <t>8,68; 11,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,95; 15,16</t>
+          <t>10,95; 15,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,05; 12,6</t>
+          <t>8,94; 12,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,5; 18,14</t>
+          <t>13,66; 18,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,92; 14,79</t>
+          <t>9,98; 14,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,56; 17,76</t>
+          <t>12,52; 18,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,75; 15,55</t>
+          <t>10,68; 15,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,9; 16,65</t>
+          <t>6,56; 16,54</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,53; 12,34</t>
+          <t>9,62; 12,42</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12,21; 15,47</t>
+          <t>12,2; 15,38</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,28; 13,26</t>
+          <t>10,36; 13,21</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10,01; 16,5</t>
+          <t>9,47; 16,41</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,68; 14,07</t>
+          <t>7,64; 13,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,65; 15,45</t>
+          <t>9,69; 15,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11,06; 16,62</t>
+          <t>10,8; 16,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,64; 21,42</t>
+          <t>14,57; 21,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,26; 18,1</t>
+          <t>11,89; 17,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,1; 30,87</t>
+          <t>24,34; 30,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,43; 26,77</t>
+          <t>20,0; 26,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>17,75; 27,42</t>
+          <t>17,98; 27,4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,81; 15,28</t>
+          <t>10,93; 15,28</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19,19; 23,88</t>
+          <t>19,36; 24,06</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16,6; 21,05</t>
+          <t>16,85; 21,05</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,98; 24,13</t>
+          <t>17,58; 24,14</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,59; 5,55</t>
+          <t>1,54; 5,56</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,8; 6,8</t>
+          <t>1,86; 6,93</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,38; 4,36</t>
+          <t>0,59; 4,17</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,16; 5,37</t>
+          <t>1,17; 6,14</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15,56; 20,11</t>
+          <t>15,44; 19,73</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20,42; 25,7</t>
+          <t>20,53; 25,77</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19,1; 24,32</t>
+          <t>18,78; 24,35</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>21,86; 27,0</t>
+          <t>22,18; 27,32</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13,14; 16,74</t>
+          <t>13,13; 16,74</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>17,19; 21,39</t>
+          <t>17,23; 21,65</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15,27; 19,69</t>
+          <t>15,35; 19,78</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17,0; 21,27</t>
+          <t>17,12; 21,47</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,34; 9,24</t>
+          <t>7,25; 9,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,92; 12,2</t>
+          <t>9,73; 12,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,36; 10,34</t>
+          <t>8,24; 10,26</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,13; 13,29</t>
+          <t>9,34; 13,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>13,46; 15,85</t>
+          <t>13,35; 15,85</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,57; 21,24</t>
+          <t>18,4; 21,29</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,25; 18,98</t>
+          <t>16,43; 19,13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>15,09; 19,88</t>
+          <t>14,95; 19,99</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>10,62; 12,17</t>
+          <t>10,72; 12,23</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14,65; 16,4</t>
+          <t>14,61; 16,35</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12,73; 14,47</t>
+          <t>12,64; 14,44</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,1; 16,35</t>
+          <t>13,24; 16,37</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejó de hacer algunas tareas por problemas físicos</t>
+          <t>Población que dejó de hacer algunas tareas por problemas físicos (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>24073; 48963</t>
+          <t>24195; 47384</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16664; 38279</t>
+          <t>16291; 36667</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23451; 46039</t>
+          <t>23247; 46226</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29623; 52918</t>
+          <t>29705; 53027</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>26082; 49620</t>
+          <t>25792; 46907</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26503; 50640</t>
+          <t>26065; 50691</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26316; 52592</t>
+          <t>26537; 53028</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>43632; 67218</t>
+          <t>43901; 67211</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>55816; 87381</t>
+          <t>54297; 88318</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>48073; 81384</t>
+          <t>47886; 79729</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>56773; 90966</t>
+          <t>55176; 89347</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>78951; 111724</t>
+          <t>80256; 113028</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11461; 30365</t>
+          <t>11627; 29037</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31050; 59033</t>
+          <t>31109; 57702</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13234; 31817</t>
+          <t>14166; 31223</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>29576; 55140</t>
+          <t>29981; 54499</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23521; 45859</t>
+          <t>23828; 45440</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26151; 50301</t>
+          <t>26291; 50259</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25061; 51017</t>
+          <t>24968; 49850</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>41000; 61524</t>
+          <t>41144; 62564</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39873; 69852</t>
+          <t>39870; 68572</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>62981; 98073</t>
+          <t>63000; 98440</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>41876; 73261</t>
+          <t>43884; 74054</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>76567; 108179</t>
+          <t>76456; 107559</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>30078; 53996</t>
+          <t>30292; 53068</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>69491; 105864</t>
+          <t>67909; 105211</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>35064; 62024</t>
+          <t>33980; 60248</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22934; 109300</t>
+          <t>22832; 107374</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>22151; 42747</t>
+          <t>22998; 43211</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>38718; 65079</t>
+          <t>38511; 64624</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26807; 49121</t>
+          <t>26028; 48199</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>30292; 48536</t>
+          <t>30257; 48952</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>57212; 87569</t>
+          <t>57516; 89337</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>115207; 158634</t>
+          <t>113991; 161255</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>68661; 103580</t>
+          <t>69356; 104225</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>40442; 150539</t>
+          <t>40394; 150006</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>106630; 147243</t>
+          <t>107462; 146797</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>126956; 175726</t>
+          <t>126921; 177567</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>104007; 144882</t>
+          <t>102787; 147941</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>139510; 187496</t>
+          <t>141166; 187786</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>70877; 105660</t>
+          <t>71286; 106926</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>96297; 136144</t>
+          <t>95990; 138611</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>88756; 128453</t>
+          <t>88193; 128153</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>67491; 162754</t>
+          <t>64175; 161700</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>186035; 240994</t>
+          <t>187920; 242506</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>235199; 297936</t>
+          <t>234975; 296215</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>203167; 261935</t>
+          <t>204594; 260963</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>201301; 331867</t>
+          <t>190356; 330051</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>26905; 49340</t>
+          <t>26776; 48909</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>49287; 78862</t>
+          <t>49497; 81646</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>68666; 103190</t>
+          <t>67010; 99409</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>69401; 101513</t>
+          <t>69071; 100843</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>69716; 102956</t>
+          <t>67609; 100911</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>183507; 235076</t>
+          <t>185354; 235077</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>150802; 197653</t>
+          <t>147677; 195992</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>149158; 230423</t>
+          <t>151101; 230250</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>99395; 140452</t>
+          <t>100479; 140487</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>244179; 303774</t>
+          <t>246295; 306069</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>225583; 286009</t>
+          <t>229022; 286056</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>236287; 317062</t>
+          <t>231002; 317317</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4751; 16552</t>
+          <t>4581; 16570</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4803; 18151</t>
+          <t>4971; 18502</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1087; 12509</t>
+          <t>1691; 11960</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2784; 12913</t>
+          <t>2805; 14774</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>194282; 251077</t>
+          <t>192822; 246397</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>226067; 284557</t>
+          <t>227350; 285315</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>206630; 263098</t>
+          <t>203224; 263476</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>166409; 205571</t>
+          <t>168878; 208013</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>203223; 258968</t>
+          <t>203151; 258892</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>236277; 293910</t>
+          <t>236721; 297504</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>209017; 269623</t>
+          <t>210159; 270878</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>170304; 213081</t>
+          <t>171501; 215129</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>240096; 302282</t>
+          <t>237248; 296922</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>339424; 417399</t>
+          <t>332938; 416061</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282890; 350229</t>
+          <t>278894; 347406</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>307929; 448245</t>
+          <t>315032; 445517</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>454550; 535322</t>
+          <t>450980; 535524</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>658442; 753140</t>
+          <t>652640; 754898</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>573960; 670247</t>
+          <t>580362; 675608</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>539693; 711070</t>
+          <t>534597; 714978</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>706199; 809013</t>
+          <t>712378; 813197</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1020803; 1142497</t>
+          <t>1018041; 1138906</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>880848; 1001279</t>
+          <t>874257; 998584</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>910531; 1136134</t>
+          <t>920120; 1137399</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P0902-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P0902-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,11; 10,0</t>
+          <t>5,12; 10,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,73; 8,39</t>
+          <t>3,82; 8,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,42; 10,77</t>
+          <t>5,26; 10,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,88; 10,5</t>
+          <t>5,72; 10,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,41; 15,3</t>
+          <t>8,21; 15,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,29; 16,12</t>
+          <t>7,97; 15,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,65; 15,28</t>
+          <t>7,48; 15,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,81; 15,02</t>
+          <t>10,27; 15,05</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,96; 11,32</t>
+          <t>7,12; 11,23</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,37; 10,61</t>
+          <t>6,47; 10,76</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,11; 11,51</t>
+          <t>7,2; 11,69</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,42; 11,86</t>
+          <t>8,36; 11,81</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,15%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,17; 7,91</t>
+          <t>2,92; 7,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,43; 13,78</t>
+          <t>7,46; 13,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,76; 8,28</t>
+          <t>3,69; 8,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,63; 12,05</t>
+          <t>6,52; 11,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,41; 12,22</t>
+          <t>6,61; 12,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,78; 14,87</t>
+          <t>7,53; 14,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,71; 13,39</t>
+          <t>6,92; 13,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,75; 16,35</t>
+          <t>11,16; 16,51</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,4; 9,28</t>
+          <t>5,29; 9,13</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,32; 13,01</t>
+          <t>8,5; 13,21</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,86; 9,88</t>
+          <t>5,71; 9,95</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,16; 12,88</t>
+          <t>9,44; 13,17</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>16,67%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,58; 9,78</t>
+          <t>5,51; 9,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,81; 16,74</t>
+          <t>10,66; 16,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,51; 11,54</t>
+          <t>6,72; 11,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,42; 16,08</t>
+          <t>11,14; 17,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,71; 25,75</t>
+          <t>13,41; 26,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,91; 25,03</t>
+          <t>15,06; 25,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,67; 29,01</t>
+          <t>15,81; 29,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,13; 29,33</t>
+          <t>17,66; 28,56</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,1; 12,58</t>
+          <t>8,27; 12,5</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12,86; 18,19</t>
+          <t>12,79; 18,05</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,08; 15,15</t>
+          <t>9,93; 15,18</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,84; 17,97</t>
+          <t>14,21; 19,53</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>15,98%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,68; 11,85</t>
+          <t>8,63; 11,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,95; 15,32</t>
+          <t>10,92; 15,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,94; 12,87</t>
+          <t>8,93; 12,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,66; 18,17</t>
+          <t>13,69; 17,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,98; 14,97</t>
+          <t>9,82; 14,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,52; 18,08</t>
+          <t>12,74; 17,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,68; 15,52</t>
+          <t>10,69; 15,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,56; 16,54</t>
+          <t>14,26; 18,58</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,62; 12,42</t>
+          <t>9,56; 12,48</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12,2; 15,38</t>
+          <t>12,16; 15,54</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,36; 13,21</t>
+          <t>10,19; 13,14</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,47; 16,41</t>
+          <t>14,54; 17,59</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,98%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,64; 13,95</t>
+          <t>7,45; 14,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,69; 15,99</t>
+          <t>9,53; 15,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,8; 16,02</t>
+          <t>11,0; 16,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,57; 21,28</t>
+          <t>13,54; 19,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,89; 17,74</t>
+          <t>11,85; 18,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,34; 30,87</t>
+          <t>24,36; 31,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,0; 26,55</t>
+          <t>19,81; 26,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>17,98; 27,4</t>
+          <t>23,42; 28,16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,93; 15,28</t>
+          <t>10,99; 15,56</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19,36; 24,06</t>
+          <t>19,18; 23,75</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16,85; 21,05</t>
+          <t>16,81; 21,25</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,58; 24,14</t>
+          <t>20,1; 23,9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,4%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,54; 5,56</t>
+          <t>1,56; 5,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,86; 6,93</t>
+          <t>1,85; 6,61</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,59; 4,17</t>
+          <t>0,38; 4,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,17; 6,14</t>
+          <t>1,17; 5,4</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15,44; 19,73</t>
+          <t>15,73; 19,9</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20,53; 25,77</t>
+          <t>20,63; 25,84</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,78; 24,35</t>
+          <t>19,13; 24,48</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>22,18; 27,32</t>
+          <t>21,81; 26,65</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13,13; 16,74</t>
+          <t>13,16; 16,72</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>17,23; 21,65</t>
+          <t>17,17; 21,55</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>15,35; 19,78</t>
+          <t>15,1; 19,82</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17,12; 21,47</t>
+          <t>17,36; 21,38</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>16,24%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,25; 9,08</t>
+          <t>7,18; 9,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,73; 12,16</t>
+          <t>9,92; 12,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,24; 10,26</t>
+          <t>8,34; 10,42</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9,34; 13,21</t>
+          <t>11,54; 13,71</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>13,35; 15,85</t>
+          <t>13,41; 15,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,4; 21,29</t>
+          <t>18,48; 21,29</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,43; 19,13</t>
+          <t>16,4; 19,14</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>14,95; 19,99</t>
+          <t>18,69; 20,91</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>10,72; 12,23</t>
+          <t>10,66; 12,22</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14,61; 16,35</t>
+          <t>14,72; 16,47</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12,64; 14,44</t>
+          <t>12,66; 14,51</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,24; 16,37</t>
+          <t>15,49; 17,12</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39916</t>
+          <t>42369</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>54916</t>
+          <t>60868</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>94832</t>
+          <t>103237</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>24195; 47384</t>
+          <t>24281; 48369</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>16291; 36667</t>
+          <t>16692; 37647</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23247; 46226</t>
+          <t>22565; 46634</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29705; 53027</t>
+          <t>31495; 56334</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>25792; 46907</t>
+          <t>25174; 48422</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26065; 50691</t>
+          <t>25051; 49613</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26537; 53028</t>
+          <t>25958; 52448</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>43901; 67211</t>
+          <t>50183; 73504</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>54297; 88318</t>
+          <t>55607; 87658</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>47886; 79729</t>
+          <t>48654; 80892</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>55176; 89347</t>
+          <t>55920; 90705</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>80256; 113028</t>
+          <t>86883; 122663</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>41035</t>
+          <t>43000</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>50609</t>
+          <t>58054</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>91645</t>
+          <t>101054</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11627; 29037</t>
+          <t>10698; 28654</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>31109; 57702</t>
+          <t>31234; 57252</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14166; 31223</t>
+          <t>13913; 31303</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>29981; 54499</t>
+          <t>31521; 56847</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23828; 45440</t>
+          <t>24571; 45401</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26291; 50259</t>
+          <t>25444; 50568</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24968; 49850</t>
+          <t>25777; 50575</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>41144; 62564</t>
+          <t>47233; 69876</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39870; 68572</t>
+          <t>39114; 67448</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>63000; 98440</t>
+          <t>64299; 99982</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>43884; 74054</t>
+          <t>42832; 74556</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>76456; 107559</t>
+          <t>85578; 119385</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>63645</t>
+          <t>67214</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>38019</t>
+          <t>42563</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>101663</t>
+          <t>109777</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>30292; 53068</t>
+          <t>29902; 53831</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>67909; 105211</t>
+          <t>67022; 106235</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>33980; 60248</t>
+          <t>35086; 60556</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22832; 107374</t>
+          <t>52462; 83838</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>22998; 43211</t>
+          <t>22495; 43702</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>38511; 64624</t>
+          <t>38887; 65385</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26028; 48199</t>
+          <t>26267; 49817</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>30257; 48952</t>
+          <t>33103; 53554</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>57516; 89337</t>
+          <t>58744; 88793</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>113991; 161255</t>
+          <t>113401; 160074</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>69356; 104225</t>
+          <t>68303; 104478</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>40394; 150006</t>
+          <t>93563; 128650</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>164201</t>
+          <t>178099</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>122799</t>
+          <t>139983</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>287000</t>
+          <t>318082</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>107462; 146797</t>
+          <t>106872; 147719</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>126921; 177567</t>
+          <t>126557; 174448</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>102787; 147941</t>
+          <t>102688; 144974</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>141166; 187786</t>
+          <t>154713; 202520</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>71286; 106926</t>
+          <t>70113; 107037</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>95990; 138611</t>
+          <t>97683; 137290</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>88193; 128153</t>
+          <t>88292; 128566</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>64175; 161700</t>
+          <t>122742; 159940</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>187920; 242506</t>
+          <t>186625; 243717</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>234975; 296215</t>
+          <t>234241; 299311</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>204594; 260963</t>
+          <t>201314; 259621</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>190356; 330051</t>
+          <t>289527; 350124</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>84954</t>
+          <t>92667</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>198702</t>
+          <t>214245</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>283657</t>
+          <t>306911</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>26776; 48909</t>
+          <t>26102; 49507</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>49497; 81646</t>
+          <t>48646; 78116</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>67010; 99409</t>
+          <t>68258; 102269</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>69071; 100843</t>
+          <t>76775; 112296</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>67609; 100911</t>
+          <t>67386; 102773</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>185354; 235077</t>
+          <t>185485; 237193</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>147677; 195992</t>
+          <t>146264; 194579</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>151101; 230250</t>
+          <t>194311; 233668</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>100479; 140487</t>
+          <t>101054; 143083</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>246295; 306069</t>
+          <t>244028; 302105</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>229022; 286056</t>
+          <t>228461; 288792</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>231002; 317317</t>
+          <t>280702; 333736</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6092</t>
+          <t>5940</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>186685</t>
+          <t>203856</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>192777</t>
+          <t>209795</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4581; 16570</t>
+          <t>4638; 16192</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4971; 18502</t>
+          <t>4934; 17631</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1691; 11960</t>
+          <t>1089; 11679</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2805; 14774</t>
+          <t>2764; 12820</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>192822; 246397</t>
+          <t>196466; 248445</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>227350; 285315</t>
+          <t>228400; 286162</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>203224; 263476</t>
+          <t>207017; 264878</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>168878; 208013</t>
+          <t>184156; 225043</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>203151; 258892</t>
+          <t>203643; 258598</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>236721; 297504</t>
+          <t>235982; 296189</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>210159; 270878</t>
+          <t>206696; 271368</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>171501; 215129</t>
+          <t>187802; 231199</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>399844</t>
+          <t>429288</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>651730</t>
+          <t>719568</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1051574</t>
+          <t>1148857</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>237248; 296922</t>
+          <t>234884; 299219</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>332938; 416061</t>
+          <t>339211; 417213</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>278894; 347406</t>
+          <t>282210; 352697</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>315032; 445517</t>
+          <t>397028; 471440</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>450980; 535524</t>
+          <t>452844; 535240</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>652640; 754898</t>
+          <t>655260; 755147</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>580362; 675608</t>
+          <t>579172; 676092</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>534597; 714978</t>
+          <t>679142; 759848</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>712378; 813197</t>
+          <t>708638; 812618</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1018041; 1138906</t>
+          <t>1025365; 1147703</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>874257; 998584</t>
+          <t>875701; 1003565</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>920120; 1137399</t>
+          <t>1095388; 1210610</t>
         </is>
       </c>
     </row>
